--- a/input/industry/Installed_capacity_subregion.xlsx
+++ b/input/industry/Installed_capacity_subregion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Projekte\endemo_Projects\endemo-ENS\endemo_IND_world_branch\endemo\input\industry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4843BEBD-1B88-4C94-B0C6-FAA7620413C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3457CCF7-8068-4DE3-95EF-1C34CE3A71FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="180" windowWidth="29040" windowHeight="17640" xr2:uid="{228D4939-5C91-456A-B1AB-654004D52185}"/>
+    <workbookView xWindow="30840" yWindow="870" windowWidth="20175" windowHeight="13230" activeTab="4" xr2:uid="{228D4939-5C91-456A-B1AB-654004D52185}"/>
   </bookViews>
   <sheets>
     <sheet name="alu_prim" sheetId="25" r:id="rId1"/>
@@ -80,9 +80,6 @@
     <t>Country</t>
   </si>
   <si>
-    <t>NUTS2</t>
-  </si>
-  <si>
     <t>Belgium</t>
   </si>
   <si>
@@ -6523,6 +6520,9 @@
   </si>
   <si>
     <t>Aluminium stewardship initiative. ABRALATAS and the circular model of aluminium beverage cans in Brazil. Available at https://aluminium-stewardship.org/abralatas-the-social-aspects-of-the-circular-economy-model-of-beverage-cans-in-brazil (2022).</t>
+  </si>
+  <si>
+    <t>Subregion</t>
   </si>
 </sst>
 </file>
@@ -7006,18 +7006,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>6.574320398740177E-3</v>
@@ -7036,10 +7036,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>8.409014463504878E-3</v>
@@ -7047,10 +7047,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5">
         <v>2.7826193315597957E-3</v>
@@ -7058,10 +7058,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>1.3148640797480354E-2</v>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7091,10 +7091,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9">
         <v>2.2933675809558756E-3</v>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>2.033452588447543E-2</v>
@@ -7113,10 +7113,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -7124,10 +7124,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>4.1433507629269487E-3</v>
@@ -7135,10 +7135,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>3.0578234412745008E-3</v>
@@ -7146,10 +7146,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>1.788826713145583E-3</v>
@@ -7157,10 +7157,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" t="s">
         <v>76</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -7168,10 +7168,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16">
         <v>7.3387762590588015E-4</v>
@@ -7179,10 +7179,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -7190,10 +7190,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -7201,10 +7201,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>9.1734703238235027E-4</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <v>1.0702382044460754E-3</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>2.3239458153686207E-3</v>
@@ -7234,10 +7234,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22">
         <v>5.4398679020273372E-2</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C23">
         <v>3.7458337155612635E-3</v>
@@ -7256,10 +7256,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C24">
         <v>6.8801027428676267E-3</v>
@@ -7267,10 +7267,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -7278,10 +7278,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C26">
         <v>3.8222793015931259E-3</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27">
         <v>1.5289117206372504E-2</v>
@@ -7300,10 +7300,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C28">
         <v>8.730085924838699E-3</v>
@@ -7311,10 +7311,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29">
         <v>5.0912760297220439E-3</v>
@@ -7322,10 +7322,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -7333,10 +7333,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31">
         <v>6.0697795309298842E-3</v>
@@ -7344,10 +7344,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32">
         <v>9.6627220744274229E-3</v>
@@ -7355,10 +7355,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C33">
         <v>5.5637097513989542E-2</v>
@@ -7366,10 +7366,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34">
         <v>1.1313946732715654E-2</v>
@@ -7377,10 +7377,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C35">
         <v>1.0962297036969085E-2</v>
@@ -7388,10 +7388,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C36">
         <v>1.5289117206372504E-3</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C37">
         <v>1.2231293765098002E-3</v>
@@ -7410,10 +7410,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -7421,10 +7421,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C39">
         <v>3.8528575360058707E-2</v>
@@ -7432,10 +7432,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C40">
         <v>1.5442008378436229E-2</v>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C41">
         <v>3.0578234412745005E-4</v>
@@ -7454,10 +7454,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42">
         <v>4.5867351619117511E-3</v>
@@ -7465,10 +7465,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C43">
         <v>2.4187383420481302E-2</v>
@@ -7476,10 +7476,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C44">
         <v>7.6445586031862519E-4</v>
@@ -7487,10 +7487,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45">
         <v>2.3682842552671009E-2</v>
@@ -7498,10 +7498,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C46">
         <v>1.0457756169158793E-2</v>
@@ -7509,10 +7509,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C47">
         <v>1.0702382044460754E-3</v>
@@ -7520,10 +7520,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C48">
         <v>4.7686756566675842E-2</v>
@@ -7531,10 +7531,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49">
         <v>0.5669204660122924</v>
@@ -7542,10 +7542,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C50">
         <v>3.9751704736568508E-3</v>
@@ -7553,10 +7553,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51">
         <v>4.5867351619117514E-4</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -7588,18 +7588,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -7607,10 +7607,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -7618,10 +7618,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>8.8218842276564411E-4</v>
@@ -7629,10 +7629,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7640,10 +7640,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>7.1677809349708589E-3</v>
@@ -7651,10 +7651,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>8.2705164634279144E-3</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -7673,10 +7673,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -7684,10 +7684,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -7695,10 +7695,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -7706,10 +7706,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -7717,10 +7717,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -7728,10 +7728,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14">
         <v>8.270516463427914E-7</v>
@@ -7739,10 +7739,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C15">
         <v>2.2054710569141104E-2</v>
@@ -7750,10 +7750,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>7.1677809349708589E-4</v>
@@ -7761,10 +7761,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -7772,10 +7772,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C18">
         <v>2.5914284918740799E-3</v>
@@ -7783,10 +7783,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C20">
         <v>0.38320059613882668</v>
@@ -7805,10 +7805,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -7827,10 +7827,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23">
         <v>1.1027355284570551E-4</v>
@@ -7838,10 +7838,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -7849,10 +7849,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25">
         <v>8.2705164634279144E-4</v>
@@ -7860,10 +7860,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26">
         <v>1.378419410571319E-3</v>
@@ -7871,10 +7871,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -7882,10 +7882,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -7893,10 +7893,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -7904,10 +7904,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -7915,10 +7915,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -7926,10 +7926,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C32">
         <v>1.9849239512226995E-3</v>
@@ -7937,10 +7937,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33">
         <v>1.2240364365873313E-2</v>
@@ -7948,10 +7948,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -7959,10 +7959,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>4.1997682601286952E-2</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36">
         <v>1.9242734971575613E-2</v>
@@ -7981,10 +7981,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37">
         <v>1.6541032926855828E-4</v>
@@ -7992,10 +7992,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39">
         <v>2.756838821142638E-3</v>
@@ -8014,10 +8014,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -8036,10 +8036,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -8047,10 +8047,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -8058,10 +8058,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -8069,10 +8069,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -8080,10 +8080,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46">
         <v>3.6721093097619936E-2</v>
@@ -8091,10 +8091,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C47">
         <v>5.8996350772452452E-2</v>
@@ -8102,10 +8102,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C49">
         <v>1.3232826341484663E-4</v>
@@ -8124,10 +8124,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -8135,10 +8135,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -8146,10 +8146,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -8157,10 +8157,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -8168,10 +8168,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -8190,10 +8190,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -8201,10 +8201,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -8212,10 +8212,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58">
         <v>3.3082065853711658E-2</v>
@@ -8223,10 +8223,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -8234,10 +8234,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C61">
         <v>1.378419410571319E-3</v>
@@ -8256,10 +8256,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>1.2130090813027607E-3</v>
@@ -8267,10 +8267,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -8278,10 +8278,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -8289,10 +8289,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -8311,10 +8311,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -8322,10 +8322,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -8344,10 +8344,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C70">
         <v>1.0475987520342023E-3</v>
@@ -8355,10 +8355,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C71">
         <v>9.9246197561134977E-4</v>
@@ -8366,10 +8366,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C72">
         <v>6.0650454065138033E-4</v>
@@ -8377,10 +8377,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73">
         <v>3.0325227032569017E-2</v>
@@ -8388,10 +8388,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -8399,10 +8399,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C75">
         <v>5.5136776422852757E-5</v>
@@ -8410,10 +8410,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -8421,10 +8421,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C78">
         <v>1.1027355284570551E-3</v>
@@ -8443,10 +8443,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C79">
         <v>4.9347414898453221E-2</v>
@@ -8454,10 +8454,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C80">
         <v>3.096481363907411E-2</v>
@@ -8465,10 +8465,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C81">
         <v>1.3398236670753221E-2</v>
@@ -8476,10 +8476,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -8487,10 +8487,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C83">
         <v>1.7643768455312882E-3</v>
@@ -8498,10 +8498,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" t="s">
         <v>76</v>
-      </c>
-      <c r="B84" t="s">
-        <v>77</v>
       </c>
       <c r="C84">
         <v>1.0475987520342024E-2</v>
@@ -8509,10 +8509,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -8520,10 +8520,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B87" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -8542,10 +8542,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B88" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -8553,10 +8553,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B89" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -8564,10 +8564,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -8575,10 +8575,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B91" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C91">
         <v>0.20455744052878375</v>
@@ -8586,10 +8586,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B92" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -8597,10 +8597,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B93" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C93">
         <v>7.1677809349708589E-3</v>
@@ -8608,10 +8608,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B94" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C95">
         <v>1.0917081731724846E-2</v>
@@ -8630,10 +8630,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -8641,10 +8641,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C97">
         <v>1.6541032926855828E-4</v>
@@ -8652,10 +8652,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B98" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -8663,10 +8663,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -8674,10 +8674,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -8685,10 +8685,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B101" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -8709,18 +8709,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -8728,10 +8728,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -8739,10 +8739,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8750,10 +8750,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5">
         <v>1.8750734636991371E-2</v>
@@ -8761,10 +8761,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <v>3.5174885583203817E-3</v>
@@ -8772,10 +8772,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
         <v>7.0898300119967379E-3</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -8794,10 +8794,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C9">
         <v>5.1028118638976518E-3</v>
@@ -8805,10 +8805,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10">
         <v>1.7024920752492165E-2</v>
@@ -8816,10 +8816,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11">
         <v>1.4925957919993132E-2</v>
@@ -8827,10 +8827,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12">
         <v>5.6266196996524104E-2</v>
@@ -8838,10 +8838,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>0.45042809513059268</v>
@@ -8849,10 +8849,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -8860,10 +8860,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -8871,10 +8871,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16">
         <v>6.3901757344970592E-3</v>
@@ -8882,10 +8882,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -8893,10 +8893,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18">
         <v>2.4096093317088913E-2</v>
@@ -8904,10 +8904,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -8915,10 +8915,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20">
         <v>1.134372801919478E-2</v>
@@ -8926,10 +8926,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C21">
         <v>1.3041462445357E-2</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>1.6362581369792472E-2</v>
@@ -8948,10 +8948,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>7.4233318842715834E-2</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C24">
         <v>1.7491356937491952E-2</v>
@@ -8970,10 +8970,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C25">
         <v>6.9965427749967804E-4</v>
@@ -8981,10 +8981,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C26">
         <v>3.1712996218135406E-2</v>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C27">
         <v>1.3461348299093807E-2</v>
@@ -9003,10 +9003,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C28">
         <v>2.1825481968509959E-3</v>
@@ -9014,10 +9014,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -9025,10 +9025,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -9036,10 +9036,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31">
         <v>2.6586862544987765E-4</v>
@@ -9047,10 +9047,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32">
         <v>1.5986540517445642E-2</v>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C33">
         <v>1.1520973769494699E-2</v>
@@ -9069,10 +9069,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C34">
         <v>2.4840712042822566E-2</v>
@@ -9080,10 +9080,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -9091,10 +9091,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -9102,10 +9102,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C37">
         <v>4.8985128148677462E-2</v>
@@ -9113,10 +9113,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38">
         <v>1.3526649364993775E-2</v>
@@ -9124,10 +9124,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39">
         <v>2.580138400944813E-3</v>
@@ -9135,10 +9135,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C40">
         <v>6.06367040499721E-4</v>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C41">
         <v>1.2868974344144078E-2</v>
@@ -9157,10 +9157,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>1.047615671509518E-2</v>
@@ -9168,10 +9168,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -9179,10 +9179,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -9190,10 +9190,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C45">
         <v>3.9133995921481991E-3</v>
@@ -9201,10 +9201,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C46">
         <v>1.4692739827493239E-2</v>
@@ -9212,10 +9212,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C48">
         <v>6.7633246824968874E-3</v>
@@ -9234,10 +9234,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C49">
         <v>8.9555747519958785E-4</v>
@@ -9245,10 +9245,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50">
         <v>3.5010700046083892E-2</v>
@@ -9256,10 +9256,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -9267,10 +9267,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C52">
         <v>8.6757130409960085E-3</v>
@@ -9278,10 +9278,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C53">
         <v>1.1194468439994848E-5</v>
@@ -9289,10 +9289,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C54">
         <v>4.25856236904804E-3</v>
@@ -9316,18 +9316,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="C1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2">
         <v>2.4236402294218317E-3</v>
@@ -9335,10 +9335,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3">
         <v>3.1753473943284464E-3</v>
@@ -9346,10 +9346,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C4">
         <v>1.9010428049527491E-3</v>
@@ -9357,10 +9357,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5">
         <v>2.6508565009301282E-3</v>
@@ -9368,10 +9368,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>1.4125278212099112E-2</v>
@@ -9379,10 +9379,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -9390,10 +9390,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8">
         <v>1.3254282504650642E-2</v>
@@ -9401,10 +9401,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10">
         <v>2.5015731383864623E-2</v>
@@ -9423,10 +9423,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C11">
         <v>0.36432879446862082</v>
@@ -9434,10 +9434,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -9445,10 +9445,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -9456,10 +9456,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
         <v>2.8841318730119798E-3</v>
@@ -9467,10 +9467,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -9478,10 +9478,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16">
         <v>2.6508565009301282E-3</v>
@@ -9489,10 +9489,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -9500,10 +9500,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>2.1509807036118756E-3</v>
@@ -9511,10 +9511,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19">
         <v>1.8809028696066869E-2</v>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>3.6207876640532058E-2</v>
@@ -9533,10 +9533,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -9544,10 +9544,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22">
         <v>3.8627940107146567E-3</v>
@@ -9555,10 +9555,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -9566,10 +9566,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24">
         <v>5.3073934086479639E-2</v>
@@ -9577,10 +9577,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25">
         <v>2.8591380831460671E-3</v>
@@ -9588,10 +9588,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26">
         <v>8.2479506557511708E-3</v>
@@ -9599,10 +9599,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -9610,10 +9610,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28">
         <v>9.5052140247637463E-3</v>
@@ -9621,10 +9621,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>4.3795936333224192E-2</v>
@@ -9632,10 +9632,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30">
         <v>2.3857708508371153E-3</v>
@@ -9643,10 +9643,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C31">
         <v>2.4728704215819627E-2</v>
@@ -9654,10 +9654,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32">
         <v>2.2721627150829672E-4</v>
@@ -9665,10 +9665,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C33">
         <v>3.0295502867772896E-3</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -9687,10 +9687,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C35">
         <v>1.1360813575414836E-3</v>
@@ -9698,10 +9698,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C36">
         <v>1.8806222348528626E-4</v>
@@ -9709,10 +9709,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -9720,10 +9720,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C38">
         <v>7.3807418861611719E-3</v>
@@ -9731,10 +9731,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -9742,10 +9742,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C40">
         <v>5.241121996124711E-3</v>
@@ -9753,10 +9753,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -9764,10 +9764,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C42">
         <v>2.277072376736352E-2</v>
@@ -9775,10 +9775,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43">
         <v>1.1360813575414836E-3</v>
@@ -9786,10 +9786,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -9797,10 +9797,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C45">
         <v>3.1252095993949021E-3</v>
@@ -9808,10 +9808,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46">
         <v>1.7041220363122253E-3</v>
@@ -9819,10 +9819,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47">
         <v>4.1656316443187732E-3</v>
@@ -9830,10 +9830,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C48">
         <v>2.0922373467509472E-3</v>
@@ -9841,10 +9841,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C49">
         <v>2.0070770649899543E-3</v>
@@ -9852,10 +9852,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C50">
         <v>9.1132473625470491E-4</v>
@@ -9863,10 +9863,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C51">
         <v>2.8947352990157001E-2</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C52">
         <v>3.0818100292241978E-2</v>
@@ -9885,10 +9885,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C53">
         <v>3.6165256548403895E-4</v>
@@ -9896,10 +9896,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C54">
         <v>7.1951819310960624E-3</v>
@@ -9907,10 +9907,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C55">
         <v>9.6117223052800407E-4</v>
@@ -9918,10 +9918,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -9929,10 +9929,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C57">
         <v>2.2153586472058928E-3</v>
@@ -9940,10 +9940,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C58">
         <v>1.1545163982527949E-2</v>
@@ -9951,10 +9951,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C59">
         <v>3.4380930955187098E-3</v>
@@ -9962,10 +9962,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C60">
         <v>1.3712501985525706E-2</v>
@@ -9973,10 +9973,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C61">
         <v>9.7400041719889856E-3</v>
@@ -9984,10 +9984,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C62">
         <v>3.9573500621028343E-3</v>
@@ -9995,10 +9995,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C63">
         <v>4.1656316443187732E-3</v>
@@ -10006,10 +10006,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C64">
         <v>8.5433318087119563E-3</v>
@@ -10017,10 +10017,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65">
         <v>0.17781566714453453</v>
@@ -10028,10 +10028,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66">
         <v>2.2721627150829671E-3</v>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C67">
         <v>1.1588029846923132E-3</v>
@@ -10063,18 +10063,18 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>237</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2">
         <v>9.9821410422081219E-4</v>
@@ -10082,10 +10082,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3">
         <v>2.6225806919983156E-3</v>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4">
         <v>0.11288894051369912</v>
@@ -10104,10 +10104,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5">
         <v>3.3213305649528839E-2</v>
@@ -10115,10 +10115,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>1.2069315987397094E-3</v>
@@ -10126,10 +10126,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1.5054883626384795E-2</v>
@@ -10137,10 +10137,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C8">
         <v>0.48691795043050251</v>
@@ -10148,10 +10148,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9">
         <v>9.2652418219040834E-3</v>
@@ -10159,10 +10159,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>1.0517546789017467E-2</v>
@@ -10170,10 +10170,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C11">
         <v>8.1073134610079423E-2</v>
@@ -10181,10 +10181,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>6.3522715723142598E-3</v>
@@ -10192,10 +10192,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>8.5301932542505773E-3</v>
@@ -10203,10 +10203,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14">
         <v>4.3286193428484311E-2</v>
@@ -10214,10 +10214,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15">
         <v>1.4201864300959738E-2</v>
@@ -10225,10 +10225,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C16">
         <v>3.1761357861571299E-3</v>
@@ -10236,10 +10236,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C17">
         <v>2.9946423126624367E-4</v>
@@ -10247,10 +10247,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C18">
         <v>1.2886036618123212E-3</v>
@@ -10258,10 +10258,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19">
         <v>4.7850754286875845E-2</v>
@@ -10269,10 +10269,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>1.3612010512101984E-3</v>
@@ -10280,10 +10280,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21">
         <v>1.1933195882276072E-2</v>
@@ -10291,10 +10291,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>2.9492689442887632E-2</v>
@@ -10302,10 +10302,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23">
         <v>6.9149013401478077E-3</v>
@@ -10313,10 +10313,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C24">
         <v>2.4501618921783571E-4</v>
@@ -10324,10 +10324,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C25">
         <v>1.8693827769953391E-3</v>
@@ -10335,10 +10335,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C26">
         <v>3.3667039333265578E-2</v>
@@ -10346,10 +10346,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C27">
         <v>1.2976783354870559E-3</v>
@@ -10357,10 +10357,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28">
         <v>1.5018584931685857E-2</v>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29">
         <v>3.638944143568597E-3</v>
@@ -10379,10 +10379,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30">
         <v>1.4365208427104962E-2</v>
@@ -10390,10 +10390,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31">
         <v>1.451947787957545E-3</v>
@@ -10417,64 +10417,64 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
         <v>161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" t="s">
         <v>53</v>
       </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" t="s">
         <v>56</v>
       </c>
-      <c r="G5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>59</v>
       </c>
-      <c r="J5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" t="s">
-        <v>60</v>
-      </c>
       <c r="L5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N5" t="s">
+        <v>71</v>
+      </c>
+      <c r="O5" t="s">
         <v>72</v>
-      </c>
-      <c r="O5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -10486,72 +10486,72 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="9"/>
       <c r="C7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="D7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
       <c r="C8" t="s">
+        <v>166</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" t="s">
         <v>169</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>170</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>171</v>
-      </c>
-      <c r="I8" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
         <v>174</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10562,78 +10562,78 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>44</v>
-      </c>
       <c r="H14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J14">
         <v>2022</v>
       </c>
       <c r="K14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G17" s="3"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G18" s="3"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G19" s="3"/>
     </row>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10653,54 +10653,54 @@
     </row>
     <row r="22" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C22" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H22" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>39</v>
-      </c>
       <c r="C23" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>178</v>
-      </c>
       <c r="F23" t="s">
+        <v>170</v>
+      </c>
+      <c r="G23" t="s">
+        <v>169</v>
+      </c>
+      <c r="H23" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" t="s">
         <v>171</v>
-      </c>
-      <c r="G23" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" t="s">
-        <v>167</v>
-      </c>
-      <c r="I23" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -10713,7 +10713,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -10724,13 +10724,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -10740,153 +10740,153 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="3"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="3"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="3"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="3"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="3"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="3"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="3"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="3"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="3"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="3"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="3"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F38" s="3"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C39" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="3"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -10897,10 +10897,10 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -10910,52 +10910,52 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G48" s="3"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G49" s="3"/>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -10964,170 +10964,170 @@
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G51" s="3"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G52" s="3"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G53" s="4"/>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C63" t="s">
+        <v>221</v>
+      </c>
+      <c r="D63" t="s">
+        <v>218</v>
+      </c>
+      <c r="E63" t="s">
         <v>222</v>
       </c>
-      <c r="D63" t="s">
-        <v>219</v>
-      </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>223</v>
-      </c>
-      <c r="F63" t="s">
-        <v>224</v>
       </c>
       <c r="G63">
         <v>2023</v>
       </c>
       <c r="H63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C64" t="s">
+        <v>224</v>
+      </c>
+      <c r="D64" t="s">
+        <v>218</v>
+      </c>
+      <c r="E64" t="s">
+        <v>222</v>
+      </c>
+      <c r="F64" t="s">
         <v>225</v>
-      </c>
-      <c r="D64" t="s">
-        <v>219</v>
-      </c>
-      <c r="E64" t="s">
-        <v>223</v>
-      </c>
-      <c r="F64" t="s">
-        <v>226</v>
       </c>
       <c r="G64">
         <v>2023</v>
       </c>
       <c r="H64" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C65" t="s">
+        <v>226</v>
+      </c>
+      <c r="D65" t="s">
+        <v>218</v>
+      </c>
+      <c r="E65" t="s">
         <v>227</v>
       </c>
-      <c r="D65" t="s">
-        <v>219</v>
-      </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>228</v>
-      </c>
-      <c r="F65" t="s">
-        <v>229</v>
       </c>
       <c r="G65">
         <v>2020</v>
       </c>
       <c r="H65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
